--- a/compressed_data_classification/src/models/best_models_result/resultados_modelos_random_mesurements.xlsx
+++ b/compressed_data_classification/src/models/best_models_result/resultados_modelos_random_mesurements.xlsx
@@ -591,7 +591,7 @@
         <v>0.7694</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9822</v>
+        <v>0.9823</v>
       </c>
       <c r="E4" t="n">
         <v>17.8553</v>

--- a/compressed_data_classification/src/models/best_models_result/resultados_modelos_random_mesurements.xlsx
+++ b/compressed_data_classification/src/models/best_models_result/resultados_modelos_random_mesurements.xlsx
@@ -475,42 +475,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0576</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4994</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="n">
-        <v>26.5953</v>
+        <v>33.3541</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.00      0.00      0.00        18
-           1       0.00      0.00      0.00        29
-           2       0.00      0.00      0.00        21
-           3       0.00      0.00      0.00        25
-           4       0.00      0.00      0.00        18
-           5       0.00      0.00      0.00        30
-           6       0.00      0.00      0.00        29
-           7       0.00      0.00      0.00        28
-           8       0.00      0.00      0.00        24
-           9       0.00      0.00      0.00        16
-          10       0.07      1.00      0.14        31
-          11       0.00      0.00      0.00        24
-          12       0.00      0.00      0.00        26
-          13       0.00      0.00      0.00        23
-          14       0.00      0.00      0.00        31
-          15       0.00      0.00      0.00        31
-          16       0.00      0.00      0.00        21
-    accuracy                           0.07       425
-   macro avg       0.00      0.06      0.01       425
-weighted avg       0.01      0.07      0.01       425
+           0       0.00      0.00      0.00        99
+           1       0.00      0.00      0.00       104
+           2       0.00      0.00      0.00       112
+           3       0.00      0.00      0.00        86
+           4       0.00      0.00      0.00        88
+           5       0.06      1.00      0.11        98
+           6       0.00      0.00      0.00       101
+           7       0.00      0.00      0.00        94
+           8       0.00      0.00      0.00        99
+           9       0.00      0.00      0.00       105
+          10       0.00      0.00      0.00       121
+          11       0.00      0.00      0.00        99
+          12       0.00      0.00      0.00        94
+          13       0.00      0.00      0.00        97
+          14       0.00      0.00      0.00       102
+          15       0.00      0.00      0.00        91
+          16       0.00      0.00      0.00       110
+    accuracy                           0.06      1700
+   macro avg       0.00      0.06      0.01      1700
+weighted avg       0.00      0.06      0.01      1700
 </t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.0573</v>
+        <v>0.0588</v>
       </c>
       <c r="H2" t="n">
         <v>0.0008</v>
@@ -526,45 +526,45 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2329</v>
+        <v>0.6418</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7839</v>
+        <v>0.962</v>
       </c>
       <c r="E3" t="n">
-        <v>34.4165</v>
+        <v>21.2041</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.75      0.50      0.60        18
-           1       0.33      0.07      0.11        29
-           2       0.14      0.05      0.07        21
-           3       0.50      0.04      0.07        25
-           4       0.05      0.89      0.10        18
-           5       0.00      0.00      0.00        30
-           6       0.89      0.55      0.68        29
-           7       0.18      0.07      0.10        28
-           8       0.25      0.08      0.12        24
-           9       1.00      1.00      1.00        16
-          10       1.00      0.58      0.73        31
-          11       0.33      0.04      0.07        24
-          12       0.50      0.04      0.07        26
-          13       1.00      0.43      0.61        23
-          14       0.00      0.00      0.00        31
-          15       0.00      0.00      0.00        31
-          16       0.29      0.19      0.23        21
-    accuracy                           0.23       425
-   macro avg       0.42      0.27      0.27       425
-weighted avg       0.41      0.23      0.25       425
+           0       0.83      0.97      0.89        99
+           1       0.67      0.50      0.57       104
+           2       0.71      0.62      0.66       112
+           3       0.74      0.76      0.75        86
+           4       0.61      0.44      0.51        88
+           5       0.71      0.48      0.57        98
+           6       0.93      0.78      0.85       101
+           7       0.61      0.37      0.46        94
+           8       0.62      0.30      0.41        99
+           9       0.99      1.00      1.00       105
+          10       0.87      0.84      0.86       121
+          11       0.63      0.40      0.49        99
+          12       0.23      0.83      0.36        94
+          13       1.00      0.97      0.98        97
+          14       0.47      0.33      0.39       102
+          15       0.53      0.34      0.41        91
+          16       0.62      0.85      0.72       110
+    accuracy                           0.64      1700
+   macro avg       0.69      0.64      0.64      1700
+weighted avg       0.70      0.64      0.65      1700
 </t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.2855</v>
+        <v>0.6122</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0173</v>
+        <v>0.009900000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -577,45 +577,45 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3765</v>
+        <v>0.6929</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8835</v>
+        <v>0.9707</v>
       </c>
       <c r="E4" t="n">
-        <v>35.5624</v>
+        <v>24.6753</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.28      0.28      0.28        18
-           1       0.75      0.21      0.32        29
-           2       0.29      0.33      0.31        21
-           3       0.44      0.32      0.37        25
-           4       0.00      0.00      0.00        18
-           5       0.25      0.07      0.11        30
-           6       0.88      0.72      0.79        29
-           7       0.35      0.29      0.31        28
-           8       0.36      0.17      0.23        24
-           9       0.43      1.00      0.60        16
-          10       0.31      0.90      0.47        31
-          11       0.38      0.12      0.19        24
-          12       0.40      0.54      0.46        26
-          13       0.29      1.00      0.46        23
-          14       0.00      0.00      0.00        31
-          15       1.00      0.26      0.41        31
-          16       0.21      0.33      0.25        21
-    accuracy                           0.38       425
-   macro avg       0.39      0.38      0.33       425
-weighted avg       0.41      0.38      0.33       425
+           0       0.58      0.92      0.71        99
+           1       0.57      0.50      0.53       104
+           2       0.63      0.54      0.58       112
+           3       0.62      0.87      0.72        86
+           4       0.65      0.70      0.67        88
+           5       0.72      0.67      0.69        98
+           6       0.88      0.91      0.89       101
+           7       0.68      0.57      0.62        94
+           8       0.69      0.70      0.69        99
+           9       0.94      1.00      0.97       105
+          10       0.72      0.72      0.72       121
+          11       0.63      0.39      0.48        99
+          12       0.90      0.66      0.76        94
+          13       0.93      0.98      0.95        97
+          14       0.46      0.36      0.41       102
+          15       0.90      0.60      0.72        91
+          16       0.50      0.69      0.58       110
+    accuracy                           0.69      1700
+   macro avg       0.70      0.69      0.69      1700
+weighted avg       0.70      0.69      0.69      1700
 </t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.366</v>
+        <v>0.6814</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0102</v>
+        <v>0.0107</v>
       </c>
     </row>
   </sheetData>

--- a/compressed_data_classification/src/models/best_models_result/resultados_modelos_random_mesurements.xlsx
+++ b/compressed_data_classification/src/models/best_models_result/resultados_modelos_random_mesurements.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,121 +471,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'mlp__activation': 'relu', 'mlp__alpha': 0.01, 'mlp__early_stopping': True, 'mlp__hidden_layer_sizes': (20, 10), 'mlp__learning_rate': 'constant', 'mlp__learning_rate_init': 0.001, 'mlp__max_iter': 5000, 'mlp__solver': 'sgd'}</t>
+          <t>{'qsvc__decision_function_shape': 'ovr', 'qsvc__probability': True}</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0576</v>
+        <v>0.6171</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>0.9619</v>
       </c>
       <c r="E2" t="n">
-        <v>33.3541</v>
+        <v>31.3588</v>
       </c>
       <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.00      0.00      0.00        99
-           1       0.00      0.00      0.00       104
-           2       0.00      0.00      0.00       112
-           3       0.00      0.00      0.00        86
-           4       0.00      0.00      0.00        88
-           5       0.06      1.00      0.11        98
-           6       0.00      0.00      0.00       101
-           7       0.00      0.00      0.00        94
-           8       0.00      0.00      0.00        99
-           9       0.00      0.00      0.00       105
-          10       0.00      0.00      0.00       121
-          11       0.00      0.00      0.00        99
-          12       0.00      0.00      0.00        94
-          13       0.00      0.00      0.00        97
-          14       0.00      0.00      0.00       102
-          15       0.00      0.00      0.00        91
-          16       0.00      0.00      0.00       110
-    accuracy                           0.06      1700
-   macro avg       0.00      0.06      0.01      1700
-weighted avg       0.00      0.06      0.01      1700
-</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0.0588</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.0008</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>{'svc_rbf__C': 1, 'svc_rbf__gamma': 0.01, 'svc_rbf__kernel': 'rbf', 'svc_rbf__probability': True, 'svc_rbf__random_state': 42}</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.6418</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.962</v>
-      </c>
-      <c r="E3" t="n">
-        <v>21.2041</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.83      0.97      0.89        99
-           1       0.67      0.50      0.57       104
-           2       0.71      0.62      0.66       112
-           3       0.74      0.76      0.75        86
-           4       0.61      0.44      0.51        88
-           5       0.71      0.48      0.57        98
-           6       0.93      0.78      0.85       101
-           7       0.61      0.37      0.46        94
-           8       0.62      0.30      0.41        99
-           9       0.99      1.00      1.00       105
-          10       0.87      0.84      0.86       121
-          11       0.63      0.40      0.49        99
-          12       0.23      0.83      0.36        94
-          13       1.00      0.97      0.98        97
-          14       0.47      0.33      0.39       102
-          15       0.53      0.34      0.41        91
-          16       0.62      0.85      0.72       110
-    accuracy                           0.64      1700
-   macro avg       0.69      0.64      0.64      1700
-weighted avg       0.70      0.64      0.65      1700
-</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0.6122</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>{'qsvc__probability': True}</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.6171</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.9615</v>
-      </c>
-      <c r="E4" t="n">
-        <v>31.3588</v>
-      </c>
-      <c r="F4" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
            0       0.40      0.93      0.56        99
@@ -611,10 +509,10 @@
 </t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G2" t="n">
         <v>0.5897</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H2" t="n">
         <v>0.0065</v>
       </c>
     </row>

--- a/compressed_data_classification/src/models/best_models_result/resultados_modelos_random_mesurements.xlsx
+++ b/compressed_data_classification/src/models/best_models_result/resultados_modelos_random_mesurements.xlsx
@@ -425,43 +425,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>melhores_parametros</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
           <t>acuracia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>roc_auc_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>mse</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>relatorio_classificacao</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>best_mean_score</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>std_best_score_k_fold</t>
         </is>
       </c>
     </row>
@@ -469,51 +454,40 @@
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>{'qsvc__decision_function_shape': 'ovr', 'qsvc__probability': True}</t>
-        </is>
+      <c r="B2" t="n">
+        <v>0.8112</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6171</v>
+        <v>0.9869</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9619</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.3588</v>
-      </c>
-      <c r="F2" t="inlineStr">
+        <v>17.1559</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.40      0.93      0.56        99
-           1       0.51      0.41      0.46       104
-           2       0.55      0.37      0.44       112
-           3       0.51      0.87      0.64        86
-           4       0.60      0.64      0.62        88
-           5       0.70      0.63      0.66        98
-           6       0.86      0.91      0.88       101
-           7       0.49      0.51      0.50        94
-           8       0.66      0.66      0.66        99
-           9       0.77      1.00      0.87       105
-          10       0.70      0.63      0.66       121
-          11       0.71      0.32      0.44        99
-          12       0.91      0.54      0.68        94
-          13       0.91      0.87      0.89        97
-          14       0.40      0.33      0.36       102
-          15       0.96      0.55      0.70        91
-          16       0.42      0.39      0.40       110
-    accuracy                           0.62      1700
-   macro avg       0.65      0.62      0.61      1700
-weighted avg       0.65      0.62      0.61      1700
+           0       0.86      1.00      0.93        99
+           1       0.73      0.51      0.60       104
+           2       0.65      0.31      0.42       112
+           3       0.92      0.98      0.95        86
+           4       0.86      0.76      0.81        88
+           5       0.95      0.89      0.92        98
+           6       1.00      0.97      0.98       101
+           7       0.84      0.80      0.82        94
+           8       0.78      0.75      0.76        99
+           9       0.95      1.00      0.98       105
+          10       0.96      0.97      0.96       121
+          11       0.59      0.74      0.65        99
+          12       0.88      0.72      0.80        94
+          13       0.98      1.00      0.99        97
+          14       0.46      0.69      0.55       102
+          15       0.90      0.76      0.82        91
+          16       0.70      0.98      0.82       110
+    accuracy                           0.81      1700
+   macro avg       0.82      0.81      0.81      1700
+weighted avg       0.82      0.81      0.81      1700
 </t>
         </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0.5897</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.0065</v>
       </c>
     </row>
   </sheetData>
